--- a/resourse/datos_cfe.xlsx
+++ b/resourse/datos_cfe.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,96 +512,96 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>155961203582</v>
+        <v>85871100565</v>
       </c>
       <c r="B2" t="n">
-        <v>251</v>
+        <v>368</v>
       </c>
       <c r="C2" t="n">
-        <v>189</v>
+        <v>495</v>
       </c>
       <c r="D2" t="n">
-        <v>158</v>
+        <v>532</v>
       </c>
       <c r="E2" t="n">
-        <v>123</v>
+        <v>517</v>
       </c>
       <c r="F2" t="n">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
-        <v>157</v>
+        <v>878</v>
       </c>
       <c r="I2" t="n">
-        <v>393</v>
+        <v>1143</v>
       </c>
       <c r="J2" t="n">
-        <v>179</v>
+        <v>1094</v>
       </c>
       <c r="K2" t="n">
-        <v>172</v>
+        <v>867</v>
       </c>
       <c r="L2" t="n">
-        <v>192</v>
+        <v>1042</v>
       </c>
       <c r="M2" t="n">
-        <v>162.15</v>
+        <v>1232.2</v>
       </c>
       <c r="N2" t="n">
-        <v>185.85</v>
+        <v>760.6799999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>02 FEB 26</t>
+          <t>29 ENE 26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>169</v>
+        <v>262</v>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>301</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>308</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>304</v>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>271</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="H3" t="n">
-        <v>88</v>
+        <v>377</v>
       </c>
       <c r="I3" t="n">
-        <v>104</v>
+        <v>431</v>
       </c>
       <c r="J3" t="n">
-        <v>104</v>
+        <v>419</v>
       </c>
       <c r="K3" t="n">
-        <v>98</v>
+        <v>371</v>
       </c>
       <c r="L3" t="n">
-        <v>113</v>
+        <v>405</v>
       </c>
       <c r="M3" t="n">
-        <v>87</v>
+        <v>442</v>
       </c>
       <c r="N3" t="n">
-        <v>101.08</v>
+        <v>350.92</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -704,337 +704,337 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>158991201397</v>
+        <v>85871100565</v>
       </c>
       <c r="B6" t="n">
-        <v>566</v>
+        <v>368</v>
       </c>
       <c r="C6" t="n">
-        <v>1296</v>
+        <v>495</v>
       </c>
       <c r="D6" t="n">
-        <v>1172</v>
+        <v>532</v>
       </c>
       <c r="E6" t="n">
-        <v>1077</v>
+        <v>517</v>
       </c>
       <c r="F6" t="n">
-        <v>906</v>
+        <v>360</v>
       </c>
       <c r="G6" t="n">
-        <v>733</v>
+        <v>600</v>
       </c>
       <c r="H6" t="n">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="I6" t="n">
-        <v>1154</v>
+        <v>1143</v>
       </c>
       <c r="J6" t="n">
-        <v>1059</v>
+        <v>1094</v>
       </c>
       <c r="K6" t="n">
-        <v>1197</v>
+        <v>867</v>
       </c>
       <c r="L6" t="n">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="M6" t="n">
-        <v>994.9299999999999</v>
+        <v>1232.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1008.08</v>
+        <v>760.6799999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>24 ENE 26</t>
+          <t>29 ENE 26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="C7" t="n">
-        <v>483</v>
+        <v>301</v>
       </c>
       <c r="D7" t="n">
-        <v>452</v>
+        <v>308</v>
       </c>
       <c r="E7" t="n">
-        <v>428</v>
+        <v>304</v>
       </c>
       <c r="F7" t="n">
-        <v>387</v>
+        <v>271</v>
       </c>
       <c r="G7" t="n">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="H7" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I7" t="n">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="J7" t="n">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="K7" t="n">
-        <v>444</v>
+        <v>371</v>
       </c>
       <c r="L7" t="n">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="M7" t="n">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="N7" t="n">
-        <v>407.58</v>
+        <v>350.92</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>201191201324</v>
+        <v>158991201397</v>
       </c>
       <c r="B8" t="n">
-        <v>327</v>
+        <v>566</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>1296</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>1172</v>
       </c>
       <c r="E8" t="n">
-        <v>347</v>
+        <v>1077</v>
       </c>
       <c r="F8" t="n">
-        <v>334</v>
+        <v>906</v>
       </c>
       <c r="G8" t="n">
-        <v>315</v>
+        <v>733</v>
       </c>
       <c r="H8" t="n">
-        <v>367</v>
+        <v>886</v>
       </c>
       <c r="I8" t="n">
-        <v>395</v>
+        <v>1154</v>
       </c>
       <c r="J8" t="n">
-        <v>193</v>
+        <v>1059</v>
       </c>
       <c r="K8" t="n">
-        <v>193</v>
+        <v>1197</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="M8" t="n">
-        <v>112.49</v>
+        <v>994.9299999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>304.77</v>
+        <v>1008.08</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>10 NOV 25</t>
+          <t>24 ENE 26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>222</v>
+        <v>312</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>483</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>452</v>
       </c>
       <c r="E9" t="n">
-        <v>231</v>
+        <v>428</v>
       </c>
       <c r="F9" t="n">
-        <v>220</v>
+        <v>387</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>346</v>
       </c>
       <c r="H9" t="n">
-        <v>238</v>
+        <v>379</v>
       </c>
       <c r="I9" t="n">
-        <v>255</v>
+        <v>438</v>
       </c>
       <c r="J9" t="n">
-        <v>115</v>
+        <v>415</v>
       </c>
       <c r="K9" t="n">
-        <v>115</v>
+        <v>444</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
       <c r="N9" t="n">
-        <v>193</v>
+        <v>407.58</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="n">
+        <v>201191201324</v>
+      </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>112.49</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>304.77</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10 NOV 25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>160240201213</v>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>385.64</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>223.47</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>01 MAR 26</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1054,509 +1054,227 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>84.42</v>
+        <v>0</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>158090202254</v>
+        <v>160240201213</v>
       </c>
       <c r="B14" t="n">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C14" t="n">
-        <v>389</v>
+        <v>110</v>
       </c>
       <c r="D14" t="n">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="E14" t="n">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="F14" t="n">
-        <v>286</v>
+        <v>111</v>
       </c>
       <c r="G14" t="n">
-        <v>299</v>
+        <v>113</v>
       </c>
       <c r="H14" t="n">
-        <v>336</v>
+        <v>115</v>
       </c>
       <c r="I14" t="n">
-        <v>349</v>
+        <v>114</v>
       </c>
       <c r="J14" t="n">
-        <v>280</v>
+        <v>434</v>
       </c>
       <c r="K14" t="n">
-        <v>278</v>
+        <v>399</v>
       </c>
       <c r="L14" t="n">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="M14" t="n">
-        <v>321.08</v>
+        <v>385.64</v>
       </c>
       <c r="N14" t="n">
-        <v>311.26</v>
+        <v>223.47</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>24 ENE 26</t>
+          <t>01 MAR 26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>264</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>197</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>225</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>179</v>
+        <v>276</v>
       </c>
       <c r="K15" t="n">
-        <v>176</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="M15" t="n">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="N15" t="n">
-        <v>203.42</v>
+        <v>84.42</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>155791102042</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>085871100565</t>
+        </is>
       </c>
       <c r="B16" t="n">
-        <v>269</v>
+        <v>368</v>
       </c>
       <c r="C16" t="n">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="D16" t="n">
-        <v>320</v>
+        <v>532</v>
       </c>
       <c r="E16" t="n">
-        <v>216</v>
+        <v>517</v>
       </c>
       <c r="F16" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="G16" t="n">
-        <v>314</v>
+        <v>600</v>
       </c>
       <c r="H16" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="I16" t="n">
-        <v>415</v>
+        <v>1143</v>
       </c>
       <c r="J16" t="n">
-        <v>248</v>
+        <v>1094</v>
       </c>
       <c r="K16" t="n">
-        <v>236</v>
+        <v>867</v>
       </c>
       <c r="L16" t="n">
-        <v>219</v>
+        <v>1042</v>
       </c>
       <c r="M16" t="n">
-        <v>366.88</v>
+        <v>1232.2</v>
       </c>
       <c r="N16" t="n">
-        <v>289.24</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
+        <v>760.6799999999999</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>22 ENE 26</t>
+          <t>29 ENE 26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="C17" t="n">
-        <v>208</v>
+        <v>301</v>
       </c>
       <c r="D17" t="n">
-        <v>224</v>
+        <v>308</v>
       </c>
       <c r="E17" t="n">
-        <v>152</v>
+        <v>304</v>
       </c>
       <c r="F17" t="n">
-        <v>167</v>
+        <v>271</v>
       </c>
       <c r="G17" t="n">
-        <v>215</v>
+        <v>320</v>
       </c>
       <c r="H17" t="n">
-        <v>208</v>
+        <v>377</v>
       </c>
       <c r="I17" t="n">
-        <v>261</v>
+        <v>431</v>
       </c>
       <c r="J17" t="n">
-        <v>149</v>
+        <v>419</v>
       </c>
       <c r="K17" t="n">
-        <v>139</v>
+        <v>371</v>
       </c>
       <c r="L17" t="n">
-        <v>125</v>
+        <v>405</v>
       </c>
       <c r="M17" t="n">
-        <v>223</v>
+        <v>442</v>
       </c>
       <c r="N17" t="n">
-        <v>188.5</v>
+        <v>350.92</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>85871100565</v>
-      </c>
-      <c r="B20" t="n">
-        <v>368</v>
-      </c>
-      <c r="C20" t="n">
-        <v>495</v>
-      </c>
-      <c r="D20" t="n">
-        <v>532</v>
-      </c>
-      <c r="E20" t="n">
-        <v>517</v>
-      </c>
-      <c r="F20" t="n">
-        <v>360</v>
-      </c>
-      <c r="G20" t="n">
-        <v>600</v>
-      </c>
-      <c r="H20" t="n">
-        <v>878</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1143</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1094</v>
-      </c>
-      <c r="K20" t="n">
-        <v>867</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1042</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1232.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>760.6799999999999</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>29 ENE 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="n">
-        <v>262</v>
-      </c>
-      <c r="C21" t="n">
-        <v>301</v>
-      </c>
-      <c r="D21" t="n">
-        <v>308</v>
-      </c>
-      <c r="E21" t="n">
-        <v>304</v>
-      </c>
-      <c r="F21" t="n">
-        <v>271</v>
-      </c>
-      <c r="G21" t="n">
-        <v>320</v>
-      </c>
-      <c r="H21" t="n">
-        <v>377</v>
-      </c>
-      <c r="I21" t="n">
-        <v>431</v>
-      </c>
-      <c r="J21" t="n">
-        <v>419</v>
-      </c>
-      <c r="K21" t="n">
-        <v>371</v>
-      </c>
-      <c r="L21" t="n">
-        <v>405</v>
-      </c>
-      <c r="M21" t="n">
-        <v>442</v>
-      </c>
-      <c r="N21" t="n">
-        <v>350.92</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>201191201324</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>327</v>
-      </c>
-      <c r="C22" t="n">
-        <v>381</v>
-      </c>
-      <c r="D22" t="n">
-        <v>388</v>
-      </c>
-      <c r="E22" t="n">
-        <v>347</v>
-      </c>
-      <c r="F22" t="n">
-        <v>334</v>
-      </c>
-      <c r="G22" t="n">
-        <v>315</v>
-      </c>
-      <c r="H22" t="n">
-        <v>367</v>
-      </c>
-      <c r="I22" t="n">
-        <v>395</v>
-      </c>
-      <c r="J22" t="n">
-        <v>193</v>
-      </c>
-      <c r="K22" t="n">
-        <v>193</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>112.49</v>
-      </c>
-      <c r="N22" t="n">
-        <v>304.77</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>10 NOV 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="n">
-        <v>222</v>
-      </c>
-      <c r="C23" t="n">
-        <v>258</v>
-      </c>
-      <c r="D23" t="n">
-        <v>261</v>
-      </c>
-      <c r="E23" t="n">
-        <v>231</v>
-      </c>
-      <c r="F23" t="n">
-        <v>220</v>
-      </c>
-      <c r="G23" t="n">
-        <v>205</v>
-      </c>
-      <c r="H23" t="n">
-        <v>238</v>
-      </c>
-      <c r="I23" t="n">
-        <v>255</v>
-      </c>
-      <c r="J23" t="n">
-        <v>115</v>
-      </c>
-      <c r="K23" t="n">
-        <v>115</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>193</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
